--- a/data/history/CyberJobs_20062026.xlsx
+++ b/data/history/CyberJobs_20062026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyber Jobs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cyber Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -83,19 +80,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -131,30 +122,30 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -522,15 +513,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="77" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="455" customWidth="1" min="6" max="6"/>
+    <col width="73" customWidth="1" min="4" max="4"/>
+    <col width="287" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -544,7 +535,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report Generated: June 20, 2026 - 09:10 PM | Total Jobs: 18</t>
+          <t>Report Generated: June 20, 2026 - 07:49 PM | Total Jobs: 25</t>
         </is>
       </c>
     </row>
@@ -592,32 +583,32 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Insider Threat Analyst</t>
+          <t>Program Manager, Security Business Enablement</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Remote - USA</t>
+          <t>US - Remote</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>2 years | Claude: This is a legitimate insider threat/security operations role at a US-based company (Remote-USA) targeting mid-level analysts with 1-6 years of experience in threat detection and investigation.</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7917252</t>
         </is>
       </c>
     </row>
@@ -632,27 +623,27 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Principal Specialist Sales Engineer - Data Security - West/South</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>South San Francisco, CA and US-Remote</t>
+          <t>Remote - Alabama, USA; Remote - Arizona, USA; Remote - California, USA; Remote - Colorado, USA; Remote - Florida, USA; Remote - Louisiana, USA; Remote - Nevada, USA; Remote - New Mexico, USA; Remote - Oregon, USA; Remote - Tennessee, USA; Remote - Utah, USA; Remote - Washington, USA</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>5 years, 5 years | Claude: USA location (South San Francisco, CA + US-Remote), legitimate AppSec/Security Engineering role with threat modeling and secure product design responsibilities, and mid-level positioning based on mentoring and cross-team initiative expectations.</t>
+          <t>5 years, 3 years</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5132564007</t>
         </is>
       </c>
     </row>
@@ -672,7 +663,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Staff Product Security Engineer</t>
+          <t>Compliance Lead, Network Growth</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -682,12 +673,12 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Not specified (Assumed 1-6 yrs) | Claude: This is a Remote-US Product Security/AppSec role, but the "Staff" level typically requires 7+ years of experience, which exceeds the 1-6 year target range.</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/7730664003</t>
         </is>
       </c>
     </row>
@@ -702,27 +693,27 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Senior Security Engineer, Corporate Security</t>
+          <t>Security Software Engineer, Infrastructure Security (Staff or Senior)</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Austin; New York City; San Francisco; Seattle; United States</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>5 years | Claude: USA location (Seattle, WA) ✓, legitimate cybersecurity role (Security Engineering, infrastructure/application security) ✓, but "Senior" title suggests 7+ years experience which exceeds the 1-6 year requirement ✗ — however, the role description emphasizes scaling through engineering fundamentals and tooling rather than requiring distinguished-level expertise, making it potentially accessible to mid-level candidates with 4-6 years.</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7727896</t>
         </is>
       </c>
     </row>
@@ -737,27 +728,27 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Rubrik</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Staff Platform Product Manager, Platform &amp; Cloud Security</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>San Francisco, CA • New York, NY • United States</t>
+          <t>Palo Alto, CA</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>5 years | Claude: This is a legitimate US-based (remote-first, San Francisco/New York) cybersecurity role (Security Engineer with AppSec, Platform Security, Product Security focus) that targets mid-level experience without specifying 7+ years required.</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7423902?gh_jid=7423902</t>
         </is>
       </c>
     </row>
@@ -767,32 +758,32 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Senior Security Engineer - Detection and Response</t>
+          <t>Sr. Staff Product Security Engineer</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>5 years | Claude: Senior Security Engineer role in Detection and Response is a legitimate cybersecurity position located in Denver, CO (USA), though the seniority level may exceed the 1-6 year target range typical for mid-level roles.</t>
+          <t>Not specified (Assumed 1-6 yrs)</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8026646002</t>
         </is>
       </c>
     </row>
@@ -802,32 +793,32 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Compliance TPM - Device Security</t>
+          <t>Senior Associate, Business Compliance</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>San Mateo, CA United States</t>
+          <t>New York, NY, USA; San Francisco, CA, USA; Washington, DC, USA</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>5 years, 5 years | Claude: This is a US-based (San Mateo, CA) cybersecurity role in device security/compliance within the 1-6 years experience range, focusing on defensive security measures and vulnerability testing.</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8440967002?gh_jid=8440967002</t>
         </is>
       </c>
     </row>
@@ -842,27 +833,27 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Product Security Engineer</t>
+          <t>Product Marketing Manager, Privacy and Video Security</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA</t>
+          <t>San Mateo, CA United States</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>3 years | Claude: Early-career Product Security Engineer role in San Francisco, CA explicitly targeting junior-level candidates with mentorship, covering AppSec/Infrastructure/Enterprise Security domains.</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5150337007</t>
         </is>
       </c>
     </row>
@@ -877,27 +868,27 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Staff Security Detection Engineer</t>
+          <t>Channel Sales Engineer - Security, AI</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US - Remote - Atlanta - Georgia , US - Headquarters - Maryland - Columbia</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>10 years, 6 years | Claude: Staff-level role with 7+ years implied experience requirement fails criterion 3 (targets 1-6 years), but the position is USA-based and is a legitimate cybersecurity detection engineering role meeting criteria 1 and 2.</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://job-boards.greenhouse.io/tenableinc/jobs/5262487008</t>
         </is>
       </c>
     </row>
@@ -917,22 +908,22 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Security Engineer, Detection &amp; Response</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Bellevue, WA</t>
+          <t>Menlo Park, CA</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Assumed mid-level senior | Claude: USA location (Bellevue, WA) ✓, legitimate cloud security role ✓, but "Senior" title typically implies 7+ years experience which exceeds the 1-6 year requirement ✗ — however, this is borderline and the role may accept mid-level candidates; recommend verifying experience requirements in full posting.</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/7697725?t=gh_src=&amp;gh_jid=7697725</t>
         </is>
       </c>
     </row>
@@ -942,17 +933,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Brex</t>
+          <t>Elastic</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer (Remote)</t>
+          <t>Security Sales Executive</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -962,12 +953,12 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>5 years | Claude: USA remote role + legitimate AppSec/penetration testing position, but "Senior" title typically implies 7+ years experience, which exceeds the 1-6 year criteria—however, this is borderline and many companies use "Senior" flexibly; the core responsibilities (code reviews, design reviews, pen testing, vulnerability management) are clearly cybersecurity roles that could be filled by strong mid-level candidates (4-6 years).</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://jobs.elastic.co/jobs?gh_jid=7585897&amp;gh_jid=7585897</t>
         </is>
       </c>
     </row>
@@ -977,32 +968,32 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Brex</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Security Engineer</t>
+          <t>Compliance Manager, Marketing</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Seattle, Washington, United States</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Assumed mid-level senior | Claude: Remote-US role at major tech company for a legitimate infrastructure/cloud security engineering position that targets mid-to-senior level experience (1-6 years fits the lower-to-mid range of "Senior" track).</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://www.brex.com/careers/8544882002?gh_jid=8544882002</t>
         </is>
       </c>
     </row>
@@ -1012,17 +1003,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Elastic</t>
+          <t>Attentive</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Senior Security Compliance Analyst - Public Sector - Information Security</t>
+          <t>Senior Technical Product Manager, Enterprise Technology &amp; Security</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1032,12 +1023,12 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Assumed mid-level senior | Claude: Role meets all criteria: USA-based position, legitimate cybersecurity compliance role (GRC/Compliance focus with DoD IL5, RMF, NIST 800-53), and "Senior" title with deep experience requirements suggests 5-8 years experience level, which falls within the 1-6 year band for mid-to-senior progression.</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://job-boards.greenhouse.io/attentive/jobs/4261611009</t>
         </is>
       </c>
     </row>
@@ -1047,32 +1038,32 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Sr. Security Engineer - Enterprise Security</t>
+          <t>Sr Product Security Engineer</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Remote - CA</t>
+          <t>Remote Canada | Remote United States</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>4 years | Claude: This is a Sr. Security Engineer role in Remote-CA (USA), focused on legitimate security infrastructure and enterprise security engineering, though the "Senior" title suggests it may target the higher end of the 1-6 year range or slightly beyond.</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://job-boards.greenhouse.io/beyondtrust/jobs/7966643</t>
         </is>
       </c>
     </row>
@@ -1082,32 +1073,32 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>LaunchDarkly</t>
+          <t>Discord</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Product Security Engineer</t>
+          <t>Staff Software Engineer, Platform Security</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Remote - US West</t>
+          <t>San Francisco Bay Area or Remote</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>2-4 years | Claude: Product Security Engineer at LaunchDarkly is a legitimate cybersecurity role (AppSec/Product Security) located in Remote - US West, targeting mid-level experience appropriate for the 1-6 year range.</t>
+          <t>5 years, 5 years</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://job-boards.greenhouse.io/discord/jobs/8177912002</t>
         </is>
       </c>
     </row>
@@ -1122,27 +1113,27 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>1Password</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Information Security Engineer</t>
+          <t>Senior Security Engineer, GRC Automation</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Remote, US</t>
+          <t>Remote (United States | Canada)</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>5 years | Claude: This is a US-based remote Information Security Engineer role (security operations &amp; control ownership) that targets mid-level experience, meeting all three criteria.</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://jobs.ashbyhq.com/1password/739b8cc9-6c96-4afb-825e-1bf5aa5e1f00</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1143,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1162,22 +1153,22 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer II, Messaging Security Products</t>
+          <t>Senior Software Engineer - Product Engineering (Identity Security)</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Remote - USA</t>
+          <t>Hybrid - San Francisco, CA, USA</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>3 years | Claude: Remote-USA location meets criterion 1; Messaging Security Products/Email Security/SOC threat visibility is legitimate cybersecurity (criterion 2); Software Engineer II typically targets 3-6 years experience (criterion 3).</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Click to Apply</t>
+          <t>https://abnormal.ai/careers/jobs/7733721003?gh_jid=7733721003</t>
         </is>
       </c>
     </row>
@@ -1187,32 +1178,277 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Obsidian Security</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Staff Enterprise Security Engineer</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>6 years</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/obsidiansecurity/jobs/4914022008</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Datadog</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Senior Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>New York, New York, USA</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>Assumed mid-level senior | Claude: Senior AppSec role at US-based company (New York) targeting mid-to-senior level experience in application security controls and platform security engineering.</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>Click to Apply</t>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Staff Application Security Engineer</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Boston, Massachusetts, USA; New York, New York, USA</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Not specified (Assumed 1-6 yrs)</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>https://careers.datadoghq.com/detail/7777798/?gh_jid=7777798</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Dragos</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Associate Principal OT Penetration Tester</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/dragos/jobs/5160432008</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, GenAI Security</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Cato Networks</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Channel Sales Engineer, AI Security - East</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia, United States</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>4 years</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>https://www.catonetworks.com/careers/careers-post/4835838101?gh_jid=4835838101</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Security Engineer, Cloud</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>New York, NY (HQ)</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>5 years, 3 years</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/ramp/34413f8d-26bf-4bbc-8ade-eb309a0e2245</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Keeper Security</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Cryptography &amp; Secrets Management</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>El Dorado Hills, California, United States</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/keepersecurity/jobs/4091113009</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Software Engineer, Infrastructure Security</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Not specified (Assumed 1-6 yrs)</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/openai/98ad9beb-4f91-496c-bd16-ac0b2a8d5bb2</t>
         </is>
       </c>
     </row>
@@ -1236,6 +1472,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history/CyberJobs_20062026.xlsx
+++ b/data/history/CyberJobs_20062026.xlsx
@@ -513,15 +513,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="73" customWidth="1" min="4" max="4"/>
-    <col width="287" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="345" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -535,7 +535,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report Generated: June 20, 2026 - 07:49 PM | Total Jobs: 25</t>
+          <t>Report Generated: June 20, 2026 - 08:01 PM | Total Jobs: 9</t>
         </is>
       </c>
     </row>
@@ -588,27 +588,27 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Program Manager, Security Business Enablement</t>
+          <t>Sr. Software Development Engineer-AI Security</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>US - Remote</t>
+          <t>Bellevue, Washington, USA; San Jose, California, USA</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>3 years | Claude: Role is a Senior Software Development Engineer in AI Security at Zscaler's US locations (Bellevue, WA and San Jose, CA), which is a legitimate cybersecurity company, though "Senior" typically implies 5-7+ years experience—borderline on the upper end of the 1-6 year range but acceptable as mid-to-senior level.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7917252</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5146134007</t>
         </is>
       </c>
     </row>
@@ -618,32 +618,32 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Zscaler</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Principal Specialist Sales Engineer - Data Security - West/South</t>
+          <t>Senior Software Engineer, Security Platform</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Remote - Alabama, USA; Remote - Arizona, USA; Remote - California, USA; Remote - Colorado, USA; Remote - Florida, USA; Remote - Louisiana, USA; Remote - Nevada, USA; Remote - New Mexico, USA; Remote - Oregon, USA; Remote - Tennessee, USA; Remote - Utah, USA; Remote - Washington, USA</t>
+          <t>Bellevue, WA</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>5 years, 3 years</t>
+          <t>5 years | Claude: Legitimate cybersecurity role (Security Platform team building secure data pipelines, authentication, authorization, and privacy infrastructure) at USA location (Bellevue, WA), but experience level cannot be fully confirmed from excerpt provided—"Senior" title suggests 7+ years which would exceed the 1-6 year requirement.</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5132564007</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/7899482?t=gh_src=&amp;gh_jid=7899482</t>
         </is>
       </c>
     </row>
@@ -653,32 +653,32 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Compliance Lead, Network Growth</t>
+          <t>Manager, Product Security</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>San Francisco, CA, USA</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>5 years, 2 years | Claude: USA location ✓, legitimate Product Security/Cloud Security role ✓, but this is a **Manager-level position** typically requiring 7+ years experience, which exceeds the 1-6 year threshold.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/7730664003</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8526680002?gh_jid=8526680002</t>
         </is>
       </c>
     </row>
@@ -688,32 +688,32 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Dropbox</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Security Software Engineer, Infrastructure Security (Staff or Senior)</t>
+          <t>Senior Infrastructure Security Engineer</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Austin; New York City; San Francisco; Seattle; United States</t>
+          <t>Remote - US: Select locations</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Assumed mid-level senior | Claude: This is a US-based remote security engineering role at a major tech company targeting mid-to-senior level experience, which aligns with legitimate infrastructure/cloud security work within the 1-6 year experience band for mid-level candidates.</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7727896</t>
+          <t>https://jobs.dropbox.com/listing/7967465?gh_jid=7967465</t>
         </is>
       </c>
     </row>
@@ -723,32 +723,32 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Rubrik</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Staff Platform Product Manager, Platform &amp; Cloud Security</t>
+          <t>Senior Security Engineer, Offensive Security</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Palo Alto, CA</t>
+          <t>New York, New York, USA</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>3 years</t>
+          <t>5 years | Claude: Senior Security Engineer role in offensive security (red teaming/penetration testing) located in USA, though the "Senior" title suggests this may target 7+ years of experience, which is borderline for the 1-6 year criteria.</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7423902?gh_jid=7423902</t>
+          <t>https://careers.datadoghq.com/detail/7871543/?gh_jid=7871543</t>
         </is>
       </c>
     </row>
@@ -758,32 +758,32 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Brex</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Sr. Staff Product Security Engineer</t>
+          <t>Senior GRC Lead</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Not specified (Assumed 1-6 yrs)</t>
+          <t>5 years | Claude: Senior GRC Lead is a legitimate cybersecurity/information security role (GRC = Governance, Risk, and Compliance) located in San Francisco, USA, though the experience level appears to target senior/experienced candidates (7+ years implied by "Senior" title), which technically exceeds the 1-6 year threshold.</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8026646002</t>
+          <t>https://www.brex.com/careers/8378792002?gh_jid=8378792002</t>
         </is>
       </c>
     </row>
@@ -793,32 +793,32 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>1Password</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Senior Associate, Business Compliance</t>
+          <t>Senior Developer (Windows), Product Security</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>New York, NY, USA; San Francisco, CA, USA; Washington, DC, USA</t>
+          <t>Remote (United States | Canada)</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>4 years, 4 years | Claude: Senior Developer role in Product Security at 1Password targeting experienced engineers (senior-level fits 1-6 years upper range) in a legitimate cybersecurity function (security feature implementation, vulnerability resolution) with remote-US eligibility.</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8440967002?gh_jid=8440967002</t>
+          <t>https://jobs.ashbyhq.com/1password/7894002a-6096-4a67-a5db-10bea270953f</t>
         </is>
       </c>
     </row>
@@ -828,32 +828,32 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Product Marketing Manager, Privacy and Video Security</t>
+          <t>Senior SDET, API / Security</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>San Mateo, CA United States</t>
+          <t>Remote, US</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>5 years | Claude: Senior SDET role at US-remote company focused on API/security testing is a legitimate cybersecurity engineering position within the 1-6 year experience band.</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/5150337007</t>
+          <t>https://job-boards.greenhouse.io/keepersecurity/jobs/4183460009</t>
         </is>
       </c>
     </row>
@@ -863,592 +863,32 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Channel Sales Engineer - Security, AI</t>
+          <t>Security Engineer, Privacy</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>US - Remote - Atlanta - Georgia , US - Headquarters - Maryland - Columbia</t>
+          <t>New York, NY (HQ)</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>4 years, 2 years | Claude: Legitimate cybersecurity role (Privacy/Security Engineering) with 4-6 years experience requirement at a US location (New York, NY).</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/tenableinc/jobs/5262487008</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Robinhood</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Security Engineer, Detection &amp; Response</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>Menlo Park, CA</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>4 years</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/7697725?t=gh_src=&amp;gh_jid=7697725</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Elastic</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Security Sales Executive</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>5 years</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>https://jobs.elastic.co/jobs?gh_jid=7585897&amp;gh_jid=7585897</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Brex</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Compliance Manager, Marketing</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>6 years</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8544882002?gh_jid=8544882002</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Attentive</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Senior Technical Product Manager, Enterprise Technology &amp; Security</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>5 years</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/attentive/jobs/4261611009</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>BeyondTrust</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Sr Product Security Engineer</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Remote Canada | Remote United States</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>4 years</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/beyondtrust/jobs/7966643</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Discord</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Staff Software Engineer, Platform Security</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>San Francisco Bay Area or Remote</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>5 years, 5 years</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/discord/jobs/8177912002</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>1Password</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer, GRC Automation</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Remote (United States | Canada)</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>5 years</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/1password/739b8cc9-6c96-4afb-825e-1bf5aa5e1f00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Abnormal Security</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Product Engineering (Identity Security)</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Hybrid - San Francisco, CA, USA</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>5 years</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>https://abnormal.ai/careers/jobs/7733721003?gh_jid=7733721003</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Obsidian Security</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Staff Enterprise Security Engineer</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>6 years</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/obsidiansecurity/jobs/4914022008</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Staff Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>Boston, Massachusetts, USA; New York, New York, USA</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Not specified (Assumed 1-6 yrs)</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>https://careers.datadoghq.com/detail/7777798/?gh_jid=7777798</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Dragos</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Associate Principal OT Penetration Tester</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>5 years</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/dragos/jobs/5160432008</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, GenAI Security</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>5 years</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/7891887</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Cato Networks</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Channel Sales Engineer, AI Security - East</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>Atlanta, Georgia, United States</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>4 years</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>https://www.catonetworks.com/careers/careers-post/4835838101?gh_jid=4835838101</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Security Engineer, Cloud</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>New York, NY (HQ)</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>5 years, 3 years</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/ramp/34413f8d-26bf-4bbc-8ade-eb309a0e2245</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Keeper Security</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cryptography &amp; Secrets Management</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>El Dorado Hills, California, United States</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>5 years</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/keepersecurity/jobs/4091113009</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Software Engineer, Infrastructure Security</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>Remote - US</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Not specified (Assumed 1-6 yrs)</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/openai/98ad9beb-4f91-496c-bd16-ac0b2a8d5bb2</t>
+          <t>https://jobs.ashbyhq.com/ramp/95f450a1-0d38-4d58-9aac-9d7e655adc36</t>
         </is>
       </c>
     </row>
@@ -1463,22 +903,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
